--- a/data/trans_orig/P36B02_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B02_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>926170</t>
+          <t>926149</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>961808</t>
+          <t>960986</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1219670</t>
+          <t>1220058</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1252517</t>
+          <t>1254146</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2157220</t>
+          <t>2156295</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2205330</t>
+          <t>2207855</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,08%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69915</t>
+          <t>70737</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>105553</t>
+          <t>105574</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62596</t>
+          <t>60967</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95443</t>
+          <t>95055</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>141505</t>
+          <t>138980</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>189615</t>
+          <t>190540</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1550986</t>
+          <t>1549044</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1594171</t>
+          <t>1593642</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,82 +1091,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>94,16%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1457</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1487019</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1467014</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>1504953</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>93,73%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>92,47%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>94,86%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2994</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>3061253</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>3030102</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3088498</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>93,36%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>92,41%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>94,19%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1457</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1487019</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1465329</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1504130</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>93,73%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>92,36%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>94,81%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2994</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>3061253</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>3030616</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3089811</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>93,36%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>92,42%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>94,23%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>98360</t>
+          <t>98889</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>141545</t>
+          <t>143487</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,82 +1204,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>5,84%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8,48%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>99521</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>81587</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>119526</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>6,27%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>5,14%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>7,53%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>217818</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>190573</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>248969</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>6,64%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>5,81%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8,36%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>99521</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>82410</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>121211</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>6,27%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>5,19%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>7,64%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>217818</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>189260</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>248455</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>6,64%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>509614</t>
+          <t>511324</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>532388</t>
+          <t>532332</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>452095</t>
+          <t>452104</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>467385</t>
+          <t>467335</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>970208</t>
+          <t>969646</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>996658</t>
+          <t>996181</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19020</t>
+          <t>19076</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41794</t>
+          <t>40084</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>9077</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24317</t>
+          <t>24308</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31162</t>
+          <t>31639</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>57612</t>
+          <t>58174</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3010865</t>
+          <t>3011724</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3070960</t>
+          <t>3071974</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3157344</t>
+          <t>3159450</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3209454</t>
+          <t>3214503</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6182195</t>
+          <t>6188622</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6267216</t>
+          <t>6266671</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,18%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>204701</t>
+          <t>203687</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>264796</t>
+          <t>263937</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>168611</t>
+          <t>163562</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>220721</t>
+          <t>218615</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>386510</t>
+          <t>387055</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>471531</t>
+          <t>465104</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>871719</t>
+          <t>871776</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>908233</t>
+          <t>907879</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1249764</t>
+          <t>1250104</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1282088</t>
+          <t>1283327</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2131995</t>
+          <t>2134187</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2182091</t>
+          <t>2181149</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66410</t>
+          <t>66764</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>102924</t>
+          <t>102867</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53678</t>
+          <t>52439</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>86002</t>
+          <t>85662</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>128318</t>
+          <t>129260</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>178414</t>
+          <t>176222</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1823084</t>
+          <t>1822907</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1866282</t>
+          <t>1866327</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1620621</t>
+          <t>1619517</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1663046</t>
+          <t>1663224</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3456645</t>
+          <t>3455602</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3519105</t>
+          <t>3519857</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,67%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>96762</t>
+          <t>96717</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>139960</t>
+          <t>140137</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>91767</t>
+          <t>91589</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>134192</t>
+          <t>135296</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>198752</t>
+          <t>198000</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>261212</t>
+          <t>262255</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>439386</t>
+          <t>440723</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>463654</t>
+          <t>462854</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>415715</t>
+          <t>417716</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>438505</t>
+          <t>438848</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>867349</t>
+          <t>866717</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>897510</t>
+          <t>896010</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,43%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17527</t>
+          <t>18327</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41795</t>
+          <t>40458</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19222</t>
+          <t>18879</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42012</t>
+          <t>40011</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41398</t>
+          <t>42898</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>71559</t>
+          <t>72191</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3161857</t>
+          <t>3162803</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3222662</t>
+          <t>3222418</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3310105</t>
+          <t>3310519</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3367822</t>
+          <t>3366785</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6488311</t>
+          <t>6488830</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6573248</t>
+          <t>6574627</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>196206</t>
+          <t>196450</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>257011</t>
+          <t>256065</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>180484</t>
+          <t>181521</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>238201</t>
+          <t>237787</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>393927</t>
+          <t>392548</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>478864</t>
+          <t>478345</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>668669</t>
+          <t>668785</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>699989</t>
+          <t>699674</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>935613</t>
+          <t>938006</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>962337</t>
+          <t>964162</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1615802</t>
+          <t>1614701</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1655163</t>
+          <t>1657162</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52406</t>
+          <t>52721</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83726</t>
+          <t>83610</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31442</t>
+          <t>29617</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58166</t>
+          <t>55773</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>91011</t>
+          <t>89012</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>130372</t>
+          <t>131473</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1860366</t>
+          <t>1860485</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1912140</t>
+          <t>1914660</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1838349</t>
+          <t>1839630</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1882205</t>
+          <t>1880438</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3713060</t>
+          <t>3716872</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3784144</t>
+          <t>3784357</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>159295</t>
+          <t>156775</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>211069</t>
+          <t>210950</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>104009</t>
+          <t>105776</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>147865</t>
+          <t>146584</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>273505</t>
+          <t>273292</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>344589</t>
+          <t>340777</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>504971</t>
+          <t>503885</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>527012</t>
+          <t>526749</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>494505</t>
+          <t>493298</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>517938</t>
+          <t>519613</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1006554</t>
+          <t>1006863</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1039671</t>
+          <t>1040465</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,93%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19874</t>
+          <t>20137</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41915</t>
+          <t>43001</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31202</t>
+          <t>29527</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54635</t>
+          <t>55842</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56356</t>
+          <t>55562</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89473</t>
+          <t>89164</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3059384</t>
+          <t>3056391</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3125666</t>
+          <t>3122667</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3292093</t>
+          <t>3292540</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3348130</t>
+          <t>3349211</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6370552</t>
+          <t>6370577</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6457052</t>
+          <t>6456893</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>245050</t>
+          <t>248049</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>311332</t>
+          <t>314325</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>181003</t>
+          <t>179922</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>237040</t>
+          <t>236593</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>442797</t>
+          <t>442956</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>529297</t>
+          <t>529272</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>436813</t>
+          <t>489847</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>421946</t>
+          <t>472085</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>451868</t>
+          <t>506234</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>677786</t>
+          <t>735793</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>663327</t>
+          <t>722652</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>689501</t>
+          <t>748935</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1114599</t>
+          <t>1225640</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1093294</t>
+          <t>1201109</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1133989</t>
+          <t>1246461</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,0%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>78125</t>
+          <t>88682</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63070</t>
+          <t>72295</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92992</t>
+          <t>106444</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>77722</t>
+          <t>86245</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66007</t>
+          <t>73103</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92181</t>
+          <t>99386</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>155847</t>
+          <t>174927</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>136457</t>
+          <t>154106</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>177152</t>
+          <t>199458</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2034972</t>
+          <t>1948614</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1986344</t>
+          <t>1910159</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2113263</t>
+          <t>1983043</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1951748</t>
+          <t>1926212</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1739082</t>
+          <t>1897796</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2036516</t>
+          <t>1950270</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3986720</t>
+          <t>3874827</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3777893</t>
+          <t>3825760</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4088714</t>
+          <t>3920302</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>89,06%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>255355</t>
+          <t>281952</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>177064</t>
+          <t>247523</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>303983</t>
+          <t>320407</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>286075</t>
+          <t>245180</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>201307</t>
+          <t>221122</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>498741</t>
+          <t>273596</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>541430</t>
+          <t>527132</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>439436</t>
+          <t>481657</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>750257</t>
+          <t>576199</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>569652</t>
+          <t>630917</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>552772</t>
+          <t>610452</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>586486</t>
+          <t>648567</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>592655</t>
+          <t>656078</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>579418</t>
+          <t>639345</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>605406</t>
+          <t>668946</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1162307</t>
+          <t>1286995</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1140071</t>
+          <t>1262526</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1184137</t>
+          <t>1309230</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,51%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76971</t>
+          <t>80670</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60137</t>
+          <t>63020</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93851</t>
+          <t>101135</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>67808</t>
+          <t>78799</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55057</t>
+          <t>65931</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81045</t>
+          <t>95532</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>144779</t>
+          <t>159469</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>122949</t>
+          <t>137234</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>167015</t>
+          <t>183938</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3041438</t>
+          <t>3069380</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2987929</t>
+          <t>3019514</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3131048</t>
+          <t>3109389</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3222190</t>
+          <t>3318082</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3034390</t>
+          <t>3281441</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3303809</t>
+          <t>3349983</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>6263628</t>
+          <t>6387462</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6067099</t>
+          <t>6328816</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6369040</t>
+          <t>6446878</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>88,93%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>410451</t>
+          <t>451303</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>320841</t>
+          <t>411294</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>463960</t>
+          <t>501169</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>431604</t>
+          <t>410225</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>349985</t>
+          <t>378324</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>619404</t>
+          <t>446866</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>842055</t>
+          <t>861528</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>736643</t>
+          <t>802112</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1038584</t>
+          <t>920174</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
